--- a/光伏配储项目/电价数据/2026/濠江站.xlsx
+++ b/光伏配储项目/电价数据/2026/濠江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.31099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.25835</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.14495</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14193</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17485</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07367</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.17579</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17139</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25268</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24196</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.15042</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.02752</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.47893</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.12105</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.09424</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.73326</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.03046</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0168</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.6967000000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.10385</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.12391</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49275</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.25458</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.30481</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.26059</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.20298</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.45854</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.19022</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.65662</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.61742</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.25595</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.53485</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.08145999999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.22156</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.1946</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.18446</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.72611</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.6347</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.71826</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.70511</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.78055</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7705</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02724</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7649199999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.56574</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.76524</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.7922</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7689</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.7678200000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.60076</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32335</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.21233</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.24805</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.09490000000000001</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21982</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.03566</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.18595</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.25476</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.20186</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.19858</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.19382</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.18535</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.19864</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.74546</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.76764</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.79414</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.12026</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.20531</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.07779000000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.04384</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.11745</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.24159</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.26625</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.24218</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45822</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5125700000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51148</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.49064</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5294</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.51505</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6267200000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.21967</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70539</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.49981</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.49416</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.63024</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.5930800000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.4655899999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.32788</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44411</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25648</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48248</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46652</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7830199999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.03236</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.05837</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.24484</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.06758</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.02545</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66731</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50246</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.24558</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14351</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26526</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25695</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10467</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02996</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42452</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31803</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.28222</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.01974</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19488</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25133</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.00784</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21777</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25131</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20461</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.04033</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20632</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04932</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1941</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01093</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06047</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31624</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.52654</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.26635</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>-0.03468</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.76691</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87036</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6569299999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57336</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.5755399999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.15808</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18282</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26337</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32429</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.18239</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.01263</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.07873999999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.02095</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.01175</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.19399</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.01886</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="S126" t="n">
+        <v>-0.00291</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.03947999999999999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.03282</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.02909</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.24535</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>-0.00465</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.10234</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.21955</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.01302</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.10707</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.23145</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.21273</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.02047</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.00708</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.23523</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.23974</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.19408</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.20336</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.004030000000000001</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.10082</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.03736</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.006549999999999999</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.16539</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.02012</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.0699</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.00445</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.18579</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.23143</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.24161</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.00456</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.00843</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.02344</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.009630000000000001</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.02233</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.02226</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.13578</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.27874</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.02153</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.22039</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.00808</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.20863</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.00529</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.03132</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19119</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.00742</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18837</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.00613</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.01121</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.01055</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>-0.00709</v>
+      </c>
+      <c r="U127" t="n">
+        <v>-0.00526</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19316</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-0.01612</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.01661</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.00646</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.00793</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-0.01156</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.01203</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.24041</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.08603</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.01131</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.007809999999999999</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.07732</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.22723</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08993000000000001</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.004070000000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>-0.00159</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14123</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.19755</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24685</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.19781</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.22778</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.24904</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.24926</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28319</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.21733</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24625</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30493</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98985</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6256699999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49291</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.53518</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.13578</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.10297</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.13915</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52488</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.03278</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.60051</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.11117</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>-0.03322</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.006549999999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.22468</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.17253</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20397</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19599</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26757</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26632</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19785</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19516</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16002</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23833</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.19982</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.03448</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20765</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17345</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16461</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.15538</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.17694</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.23192</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.03399</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.23085</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.20806</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.21136</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.22615</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.18387</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.17335</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.22229</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.22368</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.18034</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.17061</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.16455</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.21378</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.22684</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.10839</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.23182</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.25189</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.19911</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.20007</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.02636</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23855</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31775</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.00289</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.56529</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.52637</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21162</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29843</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5032099999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.55902</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60512</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74075</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46826</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31591</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.00638</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.24467</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>-0.04163</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.20007</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.19002</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.53714</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64362</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32161</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.13376</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>-0.00021</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.14441</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.2213</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.00109</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04128</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.20733</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.20591</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.02916</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.01933</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03514</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.0337</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.18091</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.17575</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.21812</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.21694</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.07213</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.26715</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.14426</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>-0.01247</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-0.01333</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.09539</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.14691</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.07203</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.17233</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.19298</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17331</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.23806</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17354</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.00414</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20519</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16264</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.00134</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16487</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16766</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17046</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00468</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17325</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01972</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18444</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18664</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15491</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.23986</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.23863</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.00566</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.17246</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.06167</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.10716</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.03737</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00186</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>-0.03102</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.01574</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.00103</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.01087</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.20487</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.18869</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.11237</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.02812</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>-0.00161</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.04126</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.04097</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.03159</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.01805</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.04257</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>-0.0337</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.13538</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.12884</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>-0.02162</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>-0.00461</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.18745</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.13312</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.17363</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>-0.01006</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.09254999999999999</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.13474</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>-0.03045</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>-0.00757</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>-0.02991</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22462</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.03122</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.1805</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.22092</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.21686</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.07381</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.08634</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.22111</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.05236</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.18427</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.01214</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.04071</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.19189</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.22229</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27524</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18928</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18625</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.004030000000000001</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20531</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21753</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.03967</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01514</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.00178</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.00179</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01561</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.00228</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17989</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01514</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01513</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00517</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03488</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.006480000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.21256</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.07496999999999999</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.18674</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.19468</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.18756</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.00112</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.16122</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23138</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.23075</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27176</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.02892</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28309</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17565</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17025</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17469</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02371</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15662</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.02288</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.0251</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.02259</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.00561</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.19966</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8504299999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86185</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09237999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00249</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.4764</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.65354</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50371</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7376</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.8329800000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.56665</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.61955</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.71129</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7095199999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7127100000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.78926</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30997</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26869</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19769</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25726</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20694</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17313</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20246</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16749</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17024</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02426</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18829</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23736</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24612</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27793</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25852</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29384</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.15778</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.71917</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.74903</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64719</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.75547</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20259</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31838</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.57955</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72211</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6371</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5481900000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32298</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.02479</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43259</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20006</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.54018</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.17204</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.48488</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32713</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.65312</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.18831</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.09378</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.09197</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.23524</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.24345</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.16009</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33926</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.22991</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14617</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04764</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12161</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22603</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18812</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26265</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22824</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05859</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.18637</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.00179</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.22442</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15557</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25131</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.01065</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.00591</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19666</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.17309</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.11843</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.42927</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.08344</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.08413</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.10713</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.09439</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.34429</v>
       </c>
     </row>
   </sheetData>
